--- a/180/food/2026-01-22-sm.xlsx
+++ b/180/food/2026-01-22-sm.xlsx
@@ -320,7 +320,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -419,6 +419,12 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -838,8 +844,8 @@
           <t>МБОУ "ООШ с.Корен-Беной"</t>
         </is>
       </c>
-      <c r="C1" s="38" t="n"/>
-      <c r="D1" s="39" t="n"/>
+      <c r="C1" s="40" t="n"/>
+      <c r="D1" s="41" t="n"/>
       <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Отд./корп</t>
@@ -854,7 +860,7 @@
       </c>
       <c r="J1" s="11" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>22.01.2026</t>
         </is>
       </c>
     </row>
@@ -926,29 +932,33 @@
           <t>гор.блюдо</t>
         </is>
       </c>
-      <c r="C4" s="19" t="e"/>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
       <c r="D4" s="20" t="inlineStr">
         <is>
-          <t>Котлета куриная</t>
+          <t>Греча отварная</t>
         </is>
       </c>
       <c r="E4" s="21" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="F4" s="22" t="n">
         <v>18.35</v>
       </c>
-      <c r="G4" s="21" t="n">
-        <v>203</v>
-      </c>
-      <c r="H4" s="40" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I4" s="40" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="J4" s="41" t="n">
-        <v>19.6</v>
+      <c r="G4" s="42" t="n">
+        <v>149.6</v>
+      </c>
+      <c r="H4" s="42" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I4" s="42" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J4" s="43" t="n">
+        <v>25.8</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
@@ -960,31 +970,31 @@
       </c>
       <c r="C5" s="27" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>283</t>
         </is>
       </c>
       <c r="D5" s="26" t="inlineStr">
         <is>
-          <t>Греча отварная №4,3</t>
+          <t>Котлета куриная</t>
         </is>
       </c>
       <c r="E5" s="28" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F5" s="29" t="n">
         <v>12.85</v>
       </c>
-      <c r="G5" s="28" t="n">
-        <v>151</v>
-      </c>
-      <c r="H5" s="42" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="I5" s="42" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J5" s="43" t="n">
-        <v>25.8</v>
+      <c r="G5" s="44" t="n">
+        <v>210.4</v>
+      </c>
+      <c r="H5" s="44" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I5" s="44" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="J5" s="45" t="n">
+        <v>19.6</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
@@ -1001,7 +1011,7 @@
       </c>
       <c r="D6" s="26" t="inlineStr">
         <is>
-          <t>Чай с лимоном №459</t>
+          <t>Чай с лимоном</t>
         </is>
       </c>
       <c r="E6" s="28" t="n">
@@ -1011,13 +1021,13 @@
         <v>33.04</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H6" s="32" t="e"/>
-      <c r="I6" s="42" t="n">
+      <c r="I6" s="44" t="n">
         <v>0.1</v>
       </c>
-      <c r="J6" s="43" t="n">
+      <c r="J6" s="45" t="n">
         <v>9.5</v>
       </c>
     </row>
@@ -1028,7 +1038,11 @@
           <t>хлеб</t>
         </is>
       </c>
-      <c r="C7" s="27" t="e"/>
+      <c r="C7" s="27" t="inlineStr">
+        <is>
+          <t>878</t>
+        </is>
+      </c>
       <c r="D7" s="26" t="inlineStr">
         <is>
           <t>Хлеб пшеничный</t>
@@ -1040,16 +1054,16 @@
       <c r="F7" s="29" t="n">
         <v>9.18</v>
       </c>
-      <c r="G7" s="28" t="n">
-        <v>117</v>
-      </c>
-      <c r="H7" s="42" t="n">
+      <c r="G7" s="44" t="n">
+        <v>116.8</v>
+      </c>
+      <c r="H7" s="44" t="n">
         <v>3.9</v>
       </c>
-      <c r="I7" s="42" t="n">
+      <c r="I7" s="44" t="n">
         <v>0.5</v>
       </c>
-      <c r="J7" s="43" t="n">
+      <c r="J7" s="45" t="n">
         <v>24.1</v>
       </c>
     </row>
@@ -1067,7 +1081,7 @@
       </c>
       <c r="D8" s="26" t="inlineStr">
         <is>
-          <t>Яблоко №338</t>
+          <t>Яблоко</t>
         </is>
       </c>
       <c r="E8" s="28" t="n">
@@ -1076,16 +1090,16 @@
       <c r="F8" s="29" t="n">
         <v>18.35</v>
       </c>
-      <c r="G8" s="28" t="n">
-        <v>76</v>
-      </c>
-      <c r="H8" s="42" t="n">
+      <c r="G8" s="44" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="H8" s="44" t="n">
         <v>1.2</v>
       </c>
-      <c r="I8" s="42" t="n">
+      <c r="I8" s="44" t="n">
         <v>0.4</v>
       </c>
-      <c r="J8" s="43" t="n">
+      <c r="J8" s="45" t="n">
         <v>16.8</v>
       </c>
     </row>
@@ -1124,34 +1138,14 @@
           <t>закуска</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="D11" s="20" t="inlineStr">
-        <is>
-          <t>Салат из моркови с сухофруктами №24</t>
-        </is>
-      </c>
-      <c r="E11" s="21" t="n">
-        <v>80</v>
-      </c>
-      <c r="F11" s="22" t="n">
-        <v>18.35</v>
-      </c>
-      <c r="G11" s="21" t="n">
-        <v>87</v>
-      </c>
-      <c r="H11" s="40" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I11" s="40" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J11" s="41" t="n">
-        <v>11.3</v>
-      </c>
+      <c r="C11" s="19" t="e"/>
+      <c r="D11" s="20" t="e"/>
+      <c r="E11" s="34" t="e"/>
+      <c r="F11" s="34" t="e"/>
+      <c r="G11" s="34" t="e"/>
+      <c r="H11" s="34" t="e"/>
+      <c r="I11" s="34" t="e"/>
+      <c r="J11" s="35" t="e"/>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" s="25" t="e"/>
@@ -1160,34 +1154,14 @@
           <t>1 блюдо</t>
         </is>
       </c>
-      <c r="C12" s="27" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="D12" s="26" t="inlineStr">
-        <is>
-          <t>Суп с фасолью №119</t>
-        </is>
-      </c>
-      <c r="E12" s="28" t="n">
-        <v>200</v>
-      </c>
-      <c r="F12" s="29" t="n">
-        <v>27.52</v>
-      </c>
-      <c r="G12" s="28" t="n">
-        <v>241</v>
-      </c>
-      <c r="H12" s="42" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="I12" s="42" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="J12" s="43" t="n">
-        <v>17.5</v>
-      </c>
+      <c r="C12" s="27" t="e"/>
+      <c r="D12" s="26" t="e"/>
+      <c r="E12" s="32" t="e"/>
+      <c r="F12" s="32" t="e"/>
+      <c r="G12" s="32" t="e"/>
+      <c r="H12" s="32" t="e"/>
+      <c r="I12" s="32" t="e"/>
+      <c r="J12" s="33" t="e"/>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="25" t="e"/>
@@ -1196,34 +1170,14 @@
           <t>2 блюдо</t>
         </is>
       </c>
-      <c r="C13" s="27" t="inlineStr">
-        <is>
-          <t>291</t>
-        </is>
-      </c>
-      <c r="D13" s="26" t="inlineStr">
-        <is>
-          <t>Плов с курицей №291</t>
-        </is>
-      </c>
-      <c r="E13" s="28" t="n">
-        <v>120</v>
-      </c>
-      <c r="F13" s="29" t="n">
-        <v>30.53</v>
-      </c>
-      <c r="G13" s="28" t="n">
-        <v>220</v>
-      </c>
-      <c r="H13" s="42" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="I13" s="42" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="J13" s="43" t="n">
-        <v>28.6</v>
-      </c>
+      <c r="C13" s="27" t="e"/>
+      <c r="D13" s="26" t="e"/>
+      <c r="E13" s="32" t="e"/>
+      <c r="F13" s="32" t="e"/>
+      <c r="G13" s="32" t="e"/>
+      <c r="H13" s="32" t="e"/>
+      <c r="I13" s="32" t="e"/>
+      <c r="J13" s="33" t="e"/>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="25" t="e"/>
@@ -1248,32 +1202,14 @@
           <t>напиток</t>
         </is>
       </c>
-      <c r="C15" s="27" t="inlineStr">
-        <is>
-          <t>459</t>
-        </is>
-      </c>
-      <c r="D15" s="26" t="inlineStr">
-        <is>
-          <t>Чай с лимоном №459</t>
-        </is>
-      </c>
-      <c r="E15" s="28" t="n">
-        <v>200</v>
-      </c>
-      <c r="F15" s="29" t="n">
-        <v>8.17</v>
-      </c>
-      <c r="G15" s="28" t="n">
-        <v>39</v>
-      </c>
+      <c r="C15" s="27" t="e"/>
+      <c r="D15" s="26" t="e"/>
+      <c r="E15" s="32" t="e"/>
+      <c r="F15" s="32" t="e"/>
+      <c r="G15" s="32" t="e"/>
       <c r="H15" s="32" t="e"/>
-      <c r="I15" s="42" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J15" s="43" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="I15" s="32" t="e"/>
+      <c r="J15" s="33" t="e"/>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="25" t="e"/>
@@ -1283,29 +1219,13 @@
         </is>
       </c>
       <c r="C16" s="27" t="e"/>
-      <c r="D16" s="26" t="inlineStr">
-        <is>
-          <t>Хлеб пшеничный</t>
-        </is>
-      </c>
-      <c r="E16" s="28" t="n">
-        <v>100</v>
-      </c>
-      <c r="F16" s="42" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="G16" s="28" t="n">
-        <v>171</v>
-      </c>
-      <c r="H16" s="42" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="I16" s="42" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J16" s="43" t="n">
-        <v>38.6</v>
-      </c>
+      <c r="D16" s="26" t="e"/>
+      <c r="E16" s="32" t="e"/>
+      <c r="F16" s="32" t="e"/>
+      <c r="G16" s="32" t="e"/>
+      <c r="H16" s="32" t="e"/>
+      <c r="I16" s="32" t="e"/>
+      <c r="J16" s="33" t="e"/>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="25" t="e"/>
@@ -1336,16 +1256,16 @@
       <c r="J18" s="33" t="e"/>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="34" t="e"/>
-      <c r="B19" s="35" t="e"/>
-      <c r="C19" s="36" t="e"/>
-      <c r="D19" s="35" t="e"/>
-      <c r="E19" s="36" t="e"/>
-      <c r="F19" s="36" t="e"/>
-      <c r="G19" s="36" t="e"/>
-      <c r="H19" s="36" t="e"/>
-      <c r="I19" s="36" t="e"/>
-      <c r="J19" s="37" t="e"/>
+      <c r="A19" s="36" t="e"/>
+      <c r="B19" s="37" t="e"/>
+      <c r="C19" s="38" t="e"/>
+      <c r="D19" s="37" t="e"/>
+      <c r="E19" s="38" t="e"/>
+      <c r="F19" s="38" t="e"/>
+      <c r="G19" s="38" t="e"/>
+      <c r="H19" s="38" t="e"/>
+      <c r="I19" s="38" t="e"/>
+      <c r="J19" s="39" t="e"/>
     </row>
   </sheetData>
   <mergeCells count="1">
